--- a/processed_ruby_restored_xlsx/sc229_瑠璃Ｂ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc229_瑠璃Ｂ：ＥＮＤ.ss.xlsx
@@ -664,8 +664,8 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>When the break between classes comes, everyone gathers
-around Rurichiyo-chan.</t>
+          <t>When the break between classes comes, everyone
+gathers around Rurichiyo-chan.</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -803,9 +803,9 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Seeing Rin-chan fidgeting with her hands while waiting
-her turn, Nono-chan, sensing something risky, warns
-her.</t>
+          <t>Seeing Rin-chan fidgeting with her hands while
+waiting her turn, Nono-chan, sensing something risky,
+warns her.</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1294,8 +1294,8 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>...When I quietly watched over her, Miru-chan tried to
-shoo me away.</t>
+          <t>...When I quietly watched over her, Miru-chan tried
+to shoo me away.</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1446,7 +1446,8 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>「Hehe！ Ah...！ By the way, you still haven't named it？」</t>
+          <t>「Hehe！ Ah...！ By the way, you still haven't named
+it？」</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1477,8 +1478,8 @@
       <c r="B67" s="1" t="inlineStr">
         <is>
           <t>「Yeah... my relatives were all strict about putting
-'Rurichiyo' in the name, which actually made it harder
-to choose...」</t>
+'Rurichiyo' in the name, which actually made it
+harder to choose...」</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2361,8 +2362,8 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>Those are words ordinary families use casually, so why
-do they feel so awkward?</t>
+          <t>Those are words ordinary families use casually, so
+why do they feel so awkward?</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2513,8 +2514,8 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's precocious phrasing confused Nono-chan, who
-put her hands together and mimicked her.</t>
+          <t>Rin-chan's precocious phrasing confused Nono-chan,
+who put her hands together and mimicked her.</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2650,7 +2651,8 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>「Oh my... sorry, you were on the boob, weren't you...」</t>
+          <t>「Oh my... sorry, you were on the boob, weren't
+you...」</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2696,8 +2698,8 @@
       <c r="B147" s="1" t="inlineStr">
         <is>
           <t>……Watching Rurichiyo-chan as she lets out a gentle
-voice after being begged for her breasts, I can’t help
-but smile.</t>
+voice after being begged for her breasts, I can’t
+help but smile.</t>
         </is>
       </c>
       <c r="C147" t="n">

--- a/processed_ruby_restored_xlsx/sc229_瑠璃Ｂ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc229_瑠璃Ｂ：ＥＮＤ.ss.xlsx
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh... nnn—」</t>
+          <t>Nnngh... nnn—</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>...When I quietly watched over her, Miru-chan tried
+          <t>...When I quietly watched over them, Miru-chan tried
 to shoo me away.</t>
         </is>
       </c>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>「Whaaaat…！ But I'm supposed to be Daddy…」</t>
+          <t>Whaaaat…！ But I」m supposed to be Daddy…</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1446,8 +1446,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>「Hehe！ Ah...！ By the way, you still haven't named
-it？」</t>
+          <t>Hehe！ Ah...！ By the way, you still haven't named it？</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1662,7 +1661,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>「Ah, haha... thanks to both of you...」</t>
+          <t>Ah, haha... thanks to both of you...</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1692,8 +1691,8 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>「Ufufu！ Thank you both… but I'll just take the
-sentiment, if you don't mind.」</t>
+          <t>Ufufu！ Thank you both… but I'll just take the
+sentiment, if you don't mind.</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1739,7 +1738,7 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>「Even Oji-sama has my own way of thinking, you
+          <t>「Even Oji-sama has his own way of thinking, you
 know...」</t>
         </is>
       </c>
@@ -2151,7 +2150,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2287,7 +2286,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2378,7 +2377,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C126" t="n">
